--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,117 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8933e29a-c226-4d24-9175-ae4196fe5c78</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>About Ascentia Labs | Leading Software Development Company</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://ascentialabs.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>support@ascentialabs.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+61412566906, +919356385744</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ascentialabs, https://www.linkedin.com/in/anmol-rikhraj-04826395, https://www.linkedin.com/in/kalrasukhpreet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://ascentialabs.com/about-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>c5bd8d42-7e28-42e5-abb0-044b7b8ce6ac</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>About Ascentia Labs | Leading Software Development Company</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://ascentialabs.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>support@ascentialabs.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+61412566906, +919356385744</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ascentialabs, https://www.linkedin.com/in/anmol-rikhraj-04826395, https://www.linkedin.com/in/kalrasukhpreet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://ascentialabs.com/about-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>d57ca9b2-52a9-4fc9-84c3-c4879607fe9c</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>About Ascentia Labs | Leading Software Development Company</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://ascentialabs.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>support@ascentialabs.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+61412566906, +919356385744</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ascentialabs, https://www.linkedin.com/in/anmol-rikhraj-04826395, https://www.linkedin.com/in/kalrasukhpreet</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://ascentialabs.com/about-us</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
